--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:04:04+00:00</t>
+    <t>2026-10-06T07:20:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T07:20:43+00:00</t>
+    <t>2026-10-07T11:41:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T11:41:58+00:00</t>
+    <t>2026-10-07T11:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-09T07:52:45+00:00</t>
+    <t>2026-10-12T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T12:51:47+00:00</t>
+    <t>2026-10-12T13:38:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6230" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6230" uniqueCount="502">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:38:08+00:00</t>
+    <t>2026-10-15T17:10:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1255,6 +1255,10 @@
 Modellerad som string i avvaktan på mappningsverifiering. Se QUESTIONS.md.</t>
   </si>
   <si>
+    <t>getlaboratoryorderoutcome-value-choice:En och endast en av cv, pq, intervalPQ och st ska anges {cv.combine(pq).combine(intervalPQ).combine(st).count() = 1}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
     <t>SEEHDSLMLaboratoryOrderOutcome.laboratoryOrderOutcome.body.groupOfAnalyses.analysis.result.value.id</t>
   </si>
   <si>
@@ -1321,6 +1325,10 @@
   </si>
   <si>
     <t>Information om vilket referensintervall eller referensvärde som gäller för ett resultat.</t>
+  </si>
+  <si>
+    <t>getlaboratoryorderoutcome-reference-choice:Ett och endast ett av interval och description ska anges {interval.exists() xor description.exists()}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>SEEHDSLMLaboratoryOrderOutcome.laboratoryOrderOutcome.body.groupOfAnalyses.analysis.result.reference.id</t>
@@ -16413,15 +16421,15 @@
         <v>72</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>81</v>
+        <v>404</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16518,10 +16526,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16620,10 +16628,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16724,10 +16732,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16753,10 +16761,10 @@
         <v>177</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -16807,7 +16815,7 @@
         <v>72</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>73</v>
@@ -16824,10 +16832,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16850,13 +16858,13 @@
         <v>72</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -16907,7 +16915,7 @@
         <v>72</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>73</v>
@@ -16924,10 +16932,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16950,13 +16958,13 @@
         <v>72</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -17007,7 +17015,7 @@
         <v>72</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>73</v>
@@ -17024,10 +17032,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17053,10 +17061,10 @@
         <v>129</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17107,7 +17115,7 @@
         <v>72</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>73</v>
@@ -17124,10 +17132,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17153,10 +17161,10 @@
         <v>129</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17207,7 +17215,7 @@
         <v>72</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>73</v>
@@ -17224,10 +17232,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17253,10 +17261,10 @@
         <v>177</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17307,7 +17315,7 @@
         <v>72</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>73</v>
@@ -17324,10 +17332,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17353,10 +17361,10 @@
         <v>78</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17407,7 +17415,7 @@
         <v>72</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>73</v>
@@ -17419,15 +17427,15 @@
         <v>72</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>81</v>
+        <v>427</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17524,10 +17532,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17626,10 +17634,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17730,10 +17738,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17756,13 +17764,13 @@
         <v>72</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
@@ -17813,7 +17821,7 @@
         <v>72</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>73</v>
@@ -17830,10 +17838,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17859,10 +17867,10 @@
         <v>129</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
@@ -17913,7 +17921,7 @@
         <v>72</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>73</v>
@@ -17930,10 +17938,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17959,10 +17967,10 @@
         <v>129</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18013,7 +18021,7 @@
         <v>72</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>73</v>
@@ -18030,10 +18038,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18059,10 +18067,10 @@
         <v>129</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -18113,7 +18121,7 @@
         <v>72</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>73</v>
@@ -18130,10 +18138,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18159,10 +18167,10 @@
         <v>78</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -18213,7 +18221,7 @@
         <v>72</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>73</v>
@@ -18230,10 +18238,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18330,10 +18338,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18432,10 +18440,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18536,10 +18544,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -18565,10 +18573,10 @@
         <v>119</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -18619,7 +18627,7 @@
         <v>72</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>73</v>
@@ -18636,10 +18644,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -18668,7 +18676,7 @@
         <v>202</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18719,7 +18727,7 @@
         <v>72</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>73</v>
@@ -18736,10 +18744,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -18768,7 +18776,7 @@
         <v>204</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -18819,7 +18827,7 @@
         <v>72</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>83</v>
@@ -18836,10 +18844,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -18865,7 +18873,7 @@
         <v>177</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M169" t="s" s="2">
         <v>179</v>
@@ -18919,7 +18927,7 @@
         <v>72</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>73</v>
@@ -18936,10 +18944,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -18965,10 +18973,10 @@
         <v>78</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
@@ -19019,7 +19027,7 @@
         <v>72</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>73</v>
@@ -19036,10 +19044,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19136,10 +19144,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19238,10 +19246,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19342,10 +19350,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19371,10 +19379,10 @@
         <v>119</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19425,7 +19433,7 @@
         <v>72</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>73</v>
@@ -19442,10 +19450,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19474,7 +19482,7 @@
         <v>202</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -19525,7 +19533,7 @@
         <v>72</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>73</v>
@@ -19542,10 +19550,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19574,7 +19582,7 @@
         <v>204</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -19625,7 +19633,7 @@
         <v>72</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>83</v>
@@ -19642,10 +19650,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19671,7 +19679,7 @@
         <v>177</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M177" t="s" s="2">
         <v>179</v>
@@ -19725,7 +19733,7 @@
         <v>72</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>73</v>
@@ -19742,10 +19750,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19771,10 +19779,10 @@
         <v>72</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -19825,7 +19833,7 @@
         <v>72</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>73</v>
@@ -19842,10 +19850,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -19871,10 +19879,10 @@
         <v>78</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
@@ -19925,7 +19933,7 @@
         <v>72</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>83</v>
@@ -19942,10 +19950,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20042,10 +20050,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20144,10 +20152,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20248,10 +20256,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20277,10 +20285,10 @@
         <v>119</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" s="2"/>
@@ -20331,7 +20339,7 @@
         <v>72</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>73</v>
@@ -20348,10 +20356,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20377,10 +20385,10 @@
         <v>129</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -20431,7 +20439,7 @@
         <v>72</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>83</v>
@@ -20448,10 +20456,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20477,10 +20485,10 @@
         <v>78</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" s="2"/>
@@ -20531,7 +20539,7 @@
         <v>72</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>73</v>
@@ -20548,10 +20556,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20648,10 +20656,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -20750,10 +20758,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -20854,10 +20862,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -20883,10 +20891,10 @@
         <v>119</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -20937,7 +20945,7 @@
         <v>72</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>73</v>
@@ -20954,10 +20962,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21037,7 +21045,7 @@
         <v>72</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>73</v>
@@ -21054,10 +21062,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21086,7 +21094,7 @@
         <v>204</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
@@ -21137,7 +21145,7 @@
         <v>72</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>83</v>
@@ -21154,10 +21162,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21183,7 +21191,7 @@
         <v>177</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M192" t="s" s="2">
         <v>179</v>
@@ -21237,7 +21245,7 @@
         <v>72</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>73</v>
@@ -21254,10 +21262,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21283,10 +21291,10 @@
         <v>78</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -21337,7 +21345,7 @@
         <v>72</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>73</v>
@@ -21354,10 +21362,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21454,10 +21462,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21556,10 +21564,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -21660,10 +21668,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -21689,10 +21697,10 @@
         <v>129</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -21743,7 +21751,7 @@
         <v>72</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>83</v>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T17:10:15+00:00</t>
+    <t>2026-10-15T18:03:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
+++ b/StructureDefinition-SEEHDSLMLaboratoryOrderOutcome.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T18:03:33+00:00</t>
+    <t>2026-10-26T15:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
